--- a/assets/附件表格资料/矩侨和尧乐融资历程.xlsx
+++ b/assets/附件表格资料/矩侨和尧乐融资历程.xlsx
@@ -38,9 +38,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="285">
-  <si>
-    <t>上海织识智能科技有限公司 4 条融资历程信息</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="288">
+  <si>
+    <t>(尧乐)上海织识智能科技有限公司 4 条融资历程信息</t>
   </si>
   <si>
     <t>序号</t>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>天使轮</t>
+  </si>
+  <si>
+    <t>小米科技全资持股），属于民营背景的产业创投机构</t>
   </si>
   <si>
     <t>威海矩侨工业科技有限公司的 5 条融资历程信息</t>
@@ -186,6 +189,29 @@
     <t>零以创投</t>
   </si>
   <si>
+    <r>
+      <t>专注于未上市企业投资的有限合伙制创业投资基金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF202020"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，属于资本市场服务类的持牌投资机构。</t>
+    </r>
+  </si>
+  <si>
     <t>2024-03-01</t>
   </si>
   <si>
@@ -198,6 +224,9 @@
     <t>国信喜海基金</t>
   </si>
   <si>
+    <t>该基金是威海临港区政府主导设立的产业引导型基金</t>
+  </si>
+  <si>
     <t>尧乐</t>
   </si>
   <si>
@@ -378,7 +407,7 @@
     <t>团队背景</t>
   </si>
   <si>
-    <t>东华大学纺织学院背景</t>
+    <t>东华大学纺织学院背景(但是没有核心科技工程人员)</t>
   </si>
   <si>
     <t>吕莉蕴（前 Harman 首席架构师）+中科院/密歇根</t>
@@ -925,7 +954,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1195,6 +1224,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202020"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
@@ -1809,7 +1844,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1896,6 +1931,9 @@
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2311,440 +2349,449 @@
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.1583333333333" style="38" customWidth="1"/>
-    <col min="2" max="2" width="25" style="38" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="38" customWidth="1"/>
-    <col min="4" max="4" width="18.25" style="38" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="38" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="38" customWidth="1"/>
-    <col min="7" max="7" width="54.25" style="38" customWidth="1"/>
-    <col min="8" max="9" width="24" style="38" customWidth="1"/>
-    <col min="10" max="10" width="20" style="38" customWidth="1"/>
-    <col min="11" max="11" width="16" style="38" customWidth="1"/>
-    <col min="12" max="12" width="12" style="38" customWidth="1"/>
-    <col min="13" max="13" width="32" style="38" customWidth="1"/>
-    <col min="14" max="14" width="40" style="38" customWidth="1"/>
-    <col min="15" max="16384" width="8.83333333333333" style="38"/>
+    <col min="1" max="1" width="15.1583333333333" style="39" customWidth="1"/>
+    <col min="2" max="2" width="25" style="39" customWidth="1"/>
+    <col min="3" max="3" width="17.25" style="39" customWidth="1"/>
+    <col min="4" max="4" width="18.25" style="39" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="39" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="39" customWidth="1"/>
+    <col min="7" max="7" width="54.25" style="39" customWidth="1"/>
+    <col min="8" max="8" width="24" style="39" customWidth="1"/>
+    <col min="9" max="9" width="30.5" style="39" customWidth="1"/>
+    <col min="10" max="10" width="20" style="39" customWidth="1"/>
+    <col min="11" max="11" width="16" style="39" customWidth="1"/>
+    <col min="12" max="12" width="12" style="39" customWidth="1"/>
+    <col min="13" max="13" width="32" style="39" customWidth="1"/>
+    <col min="14" max="14" width="40" style="39" customWidth="1"/>
+    <col min="15" max="16384" width="8.83333333333333" style="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:14">
-      <c r="A1" s="39"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
+      <c r="A1" s="40"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
     </row>
     <row r="2" ht="3" customHeight="1" spans="1:14">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="3" ht="13" customHeight="1" spans="1:14">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
     </row>
     <row r="4" ht="2" customHeight="1" spans="1:14">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-    </row>
-    <row r="5" s="36" customFormat="1" ht="34" customHeight="1" spans="1:14">
-      <c r="A5" s="40" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+    </row>
+    <row r="5" s="37" customFormat="1" ht="34" customHeight="1" spans="1:14">
+      <c r="A5" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-    </row>
-    <row r="6" s="37" customFormat="1" ht="25" customHeight="1" spans="1:14">
-      <c r="A6" s="44" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+    </row>
+    <row r="6" s="38" customFormat="1" ht="25" customHeight="1" spans="1:14">
+      <c r="A6" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:14">
-      <c r="A7" s="45">
+      <c r="A7" s="46">
         <v>1</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D7" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="45" t="s">
+      <c r="E7" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="F7" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="45" t="s">
+      <c r="G7" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
     </row>
     <row r="8" ht="69" customHeight="1" spans="1:14">
-      <c r="A8" s="45">
+      <c r="A8" s="46">
         <v>2</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="45" t="s">
+      <c r="F8" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
     </row>
     <row r="9" ht="27" customHeight="1" spans="1:14">
-      <c r="A9" s="45">
+      <c r="A9" s="46">
         <v>3</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="45" t="s">
+      <c r="E9" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:14">
-      <c r="A10" s="45">
+      <c r="A10" s="46">
         <v>4</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="45" t="s">
+      <c r="E10" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:14">
-      <c r="A11" s="39"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
+      <c r="I10" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:14">
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
     </row>
     <row r="12" ht="39" customHeight="1" spans="1:14">
-      <c r="A12" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
+      <c r="A12" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:14">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="46" t="s">
+      <c r="G13" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="47" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" ht="71" customHeight="1" spans="1:14">
-      <c r="A14" s="47">
+      <c r="A14" s="48">
         <v>1</v>
       </c>
-      <c r="B14" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="47" t="s">
+      <c r="B14" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="47" t="s">
+      <c r="C14" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="47" t="s">
+      <c r="E14" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="47" t="s">
+      <c r="G14" s="48" t="s">
         <v>31</v>
       </c>
+      <c r="H14" s="48" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="15" ht="66" spans="1:14">
-      <c r="A15" s="47">
+      <c r="A15" s="48">
         <v>2</v>
       </c>
-      <c r="B15" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="47" t="s">
+      <c r="B15" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="47" t="s">
+      <c r="E15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="47" t="s">
+      <c r="F15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="47" t="s">
+      <c r="G15" s="48" t="s">
         <v>34</v>
       </c>
+      <c r="H15" s="48" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="16" ht="39" customHeight="1" spans="1:14">
-      <c r="A16" s="47">
+      <c r="A16" s="48">
         <v>3</v>
       </c>
-      <c r="B16" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="47" t="s">
+      <c r="B16" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="E16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="47" t="s">
+      <c r="G16" s="48" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="17" ht="14" customHeight="1" spans="1:8">
-      <c r="A17" s="47">
+      <c r="H16" s="48" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" ht="29" customHeight="1" spans="1:9">
+      <c r="A17" s="48">
         <v>4</v>
       </c>
-      <c r="B17" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="47" t="s">
+      <c r="B17" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="47" t="s">
+      <c r="D17" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="47" t="s">
+      <c r="F17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="47" t="s">
+      <c r="G17" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="28.5" spans="1:9">
+      <c r="A18" s="48">
+        <v>5</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="47" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:8">
-      <c r="A18" s="47">
-        <v>5</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="47" t="s">
+      <c r="E18" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="47" t="s">
-        <v>45</v>
+      <c r="G18" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2772,108 +2819,108 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4">
-      <c r="A1" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="30" t="s">
+      <c r="A1" s="30" t="s">
         <v>49</v>
       </c>
+      <c r="B1" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2" ht="38" customHeight="1" spans="1:4">
-      <c r="A2" s="29"/>
-      <c r="B2" s="31">
+      <c r="A2" s="30"/>
+      <c r="B2" s="32">
         <v>2019</v>
       </c>
-      <c r="C2" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>51</v>
+      <c r="C2" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
-      <c r="A3" s="29"/>
-      <c r="B3" s="31">
+      <c r="A3" s="30"/>
+      <c r="B3" s="32">
         <v>2022</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>53</v>
+      <c r="C3" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:4">
-      <c r="A4" s="29"/>
-      <c r="B4" s="31">
+      <c r="A4" s="30"/>
+      <c r="B4" s="32">
         <v>2025</v>
       </c>
-      <c r="C4" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>53</v>
+      <c r="C4" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:4">
-      <c r="A5" s="29"/>
-      <c r="B5" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>57</v>
+      <c r="A5" s="30"/>
+      <c r="B5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="39" customHeight="1" spans="1:4">
-      <c r="A6" s="29"/>
-      <c r="B6" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="31" t="s">
+      <c r="A6" s="30"/>
+      <c r="B6" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="31" t="s">
-        <v>59</v>
+      <c r="C6" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="39" customHeight="1" spans="1:4">
-      <c r="A7" s="29"/>
-      <c r="B7" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="31"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="32"/>
     </row>
     <row r="8" ht="31" customHeight="1" spans="1:4">
-      <c r="A8" s="29"/>
-      <c r="B8" s="31">
+      <c r="A8" s="30"/>
+      <c r="B8" s="32">
         <v>2026</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>62</v>
+      <c r="C8" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" ht="39" customHeight="1" spans="1:4">
-      <c r="A9" s="29"/>
-      <c r="B9" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="34"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="35"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1"/>
@@ -2889,94 +2936,94 @@
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4">
       <c r="A12" s="1"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4">
-      <c r="A13" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>49</v>
+      <c r="A13" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:4">
-      <c r="A14" s="29"/>
-      <c r="B14" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>69</v>
+      <c r="A14" s="30"/>
+      <c r="B14" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:4">
-      <c r="A15" s="29"/>
-      <c r="B15" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>53</v>
+      <c r="A15" s="30"/>
+      <c r="B15" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:4">
-      <c r="A16" s="29"/>
-      <c r="B16" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>53</v>
+      <c r="A16" s="30"/>
+      <c r="B16" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:4">
-      <c r="A17" s="29"/>
-      <c r="B17" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>55</v>
+      <c r="A17" s="30"/>
+      <c r="B17" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1" spans="1:4">
-      <c r="A18" s="29"/>
-      <c r="B18" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>78</v>
+      <c r="A18" s="30"/>
+      <c r="B18" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:4">
-      <c r="A19" s="29"/>
-      <c r="B19" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>81</v>
+      <c r="A19" s="30"/>
+      <c r="B19" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3005,144 +3052,144 @@
   <sheetData>
     <row r="1" ht="31" customHeight="1" spans="1:6">
       <c r="A1" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:6">
       <c r="A2" s="18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6">
       <c r="A3" s="18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:6">
       <c r="A4" s="18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:6">
       <c r="A5" s="18" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:6">
       <c r="A6" s="18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6">
       <c r="A7" s="18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" ht="26" customHeight="1" spans="1:6">
+    <row r="8" ht="41" customHeight="1" spans="1:6">
       <c r="A8" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>106</v>
+        <v>108</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>109</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6">
       <c r="A9" s="18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -3176,9 +3223,9 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:22">
+    <row r="1" ht="42" customHeight="1" spans="1:22">
       <c r="A1" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3197,25 +3244,25 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -3240,22 +3287,22 @@
         <v>45808</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
@@ -3280,22 +3327,22 @@
         <v>45804</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -3320,22 +3367,22 @@
         <v>45801</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -3360,22 +3407,22 @@
         <v>45797</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -3400,22 +3447,22 @@
         <v>45798</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
@@ -3440,22 +3487,22 @@
         <v>45784</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -3480,22 +3527,22 @@
         <v>45742</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -3520,22 +3567,22 @@
         <v>45735</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>11</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -3560,22 +3607,22 @@
         <v>45723</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
@@ -3600,22 +3647,22 @@
         <v>45707</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
@@ -3640,22 +3687,22 @@
         <v>45646</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -3680,22 +3727,22 @@
         <v>45626</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -3720,22 +3767,22 @@
         <v>45626</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -3760,22 +3807,22 @@
         <v>45621</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -3800,22 +3847,22 @@
         <v>45535</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
@@ -3840,22 +3887,22 @@
         <v>45527</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
@@ -3880,22 +3927,22 @@
         <v>45474</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
@@ -3920,22 +3967,22 @@
         <v>45464</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
@@ -3960,22 +4007,22 @@
         <v>45443</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
@@ -4000,22 +4047,22 @@
         <v>45326</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
@@ -4056,7 +4103,7 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:22">
       <c r="A24" s="12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -4082,7 +4129,7 @@
     </row>
     <row r="25" ht="27" customHeight="1" spans="1:22">
       <c r="A25" s="15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -4091,7 +4138,7 @@
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I25" s="15"/>
       <c r="J25" s="16"/>
@@ -4110,7 +4157,7 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:22">
       <c r="A26" s="18" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -4136,12 +4183,12 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:22">
       <c r="A27" s="20" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
       <c r="D27" s="20" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E27" s="20"/>
       <c r="F27" s="20"/>
@@ -4164,12 +4211,12 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:22">
       <c r="A28" s="20" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="20" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E28" s="20"/>
       <c r="F28" s="20"/>
@@ -4192,12 +4239,12 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:22">
       <c r="A29" s="22" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
@@ -4220,7 +4267,7 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:22">
       <c r="A30" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
@@ -4246,12 +4293,12 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:22">
       <c r="A31" s="20" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
       <c r="D31" s="20" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E31" s="20"/>
       <c r="F31" s="20"/>
@@ -4274,12 +4321,12 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:22">
       <c r="A32" s="22" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
       <c r="D32" s="22" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -4302,7 +4349,7 @@
     </row>
     <row r="33" ht="23" customHeight="1" spans="1:22">
       <c r="A33" s="18" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
@@ -4328,12 +4375,12 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:22">
       <c r="A34" s="20" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E34" s="20"/>
       <c r="F34" s="20"/>
@@ -4356,12 +4403,12 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:22">
       <c r="A35" s="20" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
       <c r="D35" s="20" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E35" s="20"/>
       <c r="F35" s="20"/>
@@ -4384,7 +4431,7 @@
     </row>
     <row r="36" ht="23" customHeight="1" spans="1:22">
       <c r="A36" s="18" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -4410,12 +4457,12 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:22">
       <c r="A37" s="22" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
       <c r="D37" s="22" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="22"/>
@@ -4438,12 +4485,12 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:22">
       <c r="A38" s="20" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E38" s="20"/>
       <c r="F38" s="20"/>
@@ -4466,12 +4513,12 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:22">
       <c r="A39" s="20" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
       <c r="D39" s="20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E39" s="20"/>
       <c r="F39" s="20"/>
@@ -4494,12 +4541,12 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:22">
       <c r="A40" s="20" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E40" s="20"/>
       <c r="F40" s="20"/>
@@ -4522,7 +4569,7 @@
     </row>
     <row r="41" ht="27" customHeight="1" spans="1:22">
       <c r="A41" s="18" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
@@ -4548,12 +4595,12 @@
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:22">
       <c r="A42" s="20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E42" s="20"/>
       <c r="F42" s="20"/>
@@ -4576,12 +4623,12 @@
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:22">
       <c r="A43" s="20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
       <c r="D43" s="20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E43" s="20"/>
       <c r="F43" s="20"/>
@@ -4604,12 +4651,12 @@
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:22">
       <c r="A44" s="20" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E44" s="20"/>
       <c r="F44" s="20"/>
@@ -4632,12 +4679,12 @@
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:22">
       <c r="A45" s="20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
       <c r="D45" s="20" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E45" s="20"/>
       <c r="F45" s="20"/>
@@ -4660,12 +4707,12 @@
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:22">
       <c r="A46" s="20" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="20" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E46" s="20"/>
       <c r="F46" s="20"/>
@@ -4688,12 +4735,12 @@
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:22">
       <c r="A47" s="22" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
       <c r="D47" s="22" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
@@ -4716,7 +4763,7 @@
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:22">
       <c r="A48" s="18" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -4742,12 +4789,12 @@
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:22">
       <c r="A49" s="22" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
       <c r="D49" s="22" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
@@ -4770,12 +4817,12 @@
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:22">
       <c r="A50" s="20" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
       <c r="D50" s="20" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E50" s="20"/>
       <c r="F50" s="20"/>
@@ -4798,12 +4845,12 @@
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:22">
       <c r="A51" s="20" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
       <c r="D51" s="20" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E51" s="20"/>
       <c r="F51" s="20"/>
@@ -4826,12 +4873,12 @@
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:22">
       <c r="A52" s="22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
       <c r="D52" s="22" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
@@ -4854,7 +4901,7 @@
     </row>
     <row r="53" ht="29" customHeight="1" spans="1:22">
       <c r="A53" s="18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
@@ -4880,12 +4927,12 @@
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:22">
       <c r="A54" s="20" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
       <c r="D54" s="20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E54" s="20"/>
       <c r="F54" s="20"/>
@@ -4908,12 +4955,12 @@
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:22">
       <c r="A55" s="20" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
       <c r="D55" s="20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E55" s="20"/>
       <c r="F55" s="20"/>
@@ -4936,12 +4983,12 @@
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:22">
       <c r="A56" s="22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
       <c r="D56" s="22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
